--- a/tools/importer/reports/import-credit-card-product.report.xlsx
+++ b/tools/importer/reports/import-credit-card-product.report.xlsx
@@ -52,7 +52,7 @@
     <t>credit-card-product</t>
   </si>
   <si>
-    <t>2026-08-07T09:18:17.720Z</t>
+    <t>2026-08-09T13:19:50.696Z</t>
   </si>
   <si>
     <t>Credit Card with Domestic Lounge Access, Dining &amp; Movie Tickets | BOBCARD Eterna</t>
